--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <r>
       <rPr>
@@ -142,7 +142,7 @@
     </r>
   </si>
   <si>
-    <t>NETWEB</t>
+    <t>AVALON</t>
   </si>
   <si>
     <t>Mandatory Input Field (Not case-sensitive)</t>
@@ -327,7 +327,19 @@
     <t>SL price may vary slightly due to slippage when using a Stop-Loss Market (SL-M) order.</t>
   </si>
   <si>
-    <t>Target Price</t>
+    <t>Target Price (T1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The primary target — and in most cases, the only target that matters.
+</t>
+  </si>
+  <si>
+    <t>Target Price (T2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The secondary target should only be used if you plan to follow a dynamic exit strategy — for example, booking 50% at T1, moving the stop loss to breakeven, and then trailing the remaining position below each new swing low until T2 is hit.
+This approach is not perfect. Some days, price will reverse after hitting T1, reducing your overall profit. On other days, the move will continue to T2 and deliver larger gains. Be prepared mentally for both outcomes.
+</t>
   </si>
   <si>
     <t>Loss Amount</t>
@@ -871,7 +883,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="32.0"/>
     <col customWidth="1" min="2" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="3" width="68.43"/>
+    <col customWidth="1" min="3" max="3" width="121.14"/>
     <col customWidth="1" min="4" max="25" width="8.71"/>
   </cols>
   <sheetData>
@@ -1198,7 +1210,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="20">
-        <v>4456.0</v>
+        <v>1362.5</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>20</v>
@@ -1231,8 +1243,8 @@
         <v>21</v>
       </c>
       <c r="B12" s="22">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(ISNUMBER(B11), B11, GOOGLEFINANCE(""NSE:""&amp;B10,""high""))"),4456.0)</f>
-        <v>4456</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(ISNUMBER(B11), B11, GOOGLEFINANCE(""NSE:""&amp;B10,""high""))"),1362.5)</f>
+        <v>1362.5</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>22</v>
@@ -1265,7 +1277,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="24">
-        <v>22.0</v>
+        <v>16.0</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>24</v>
@@ -1328,7 +1340,7 @@
       </c>
       <c r="B15" s="25">
         <f>CEILING(B13*B7, 0.1)</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>27</v>
@@ -1430,7 +1442,7 @@
       </c>
       <c r="B18" s="28">
         <f>IF(B15&gt;0,B16/B15,0)</f>
-        <v>818.1818182</v>
+        <v>1125</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>33</v>
@@ -1464,7 +1476,7 @@
       </c>
       <c r="B19" s="29">
         <f>B17/B12</f>
-        <v>454.443447</v>
+        <v>1486.238532</v>
       </c>
       <c r="C19" s="26" t="s">
         <v>35</v>
@@ -1498,7 +1510,7 @@
       </c>
       <c r="B20" s="29">
         <f>MIN(B18,B19)</f>
-        <v>454.443447</v>
+        <v>1125</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>37</v>
@@ -1561,7 +1573,7 @@
       </c>
       <c r="B22" s="32" t="str">
         <f>B10</f>
-        <v>NETWEB</v>
+        <v>AVALON</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1593,7 +1605,7 @@
       </c>
       <c r="B23" s="34">
         <f>IF(B20&gt;5, ROUND(B20/5, 0)*5, B20)</f>
-        <v>455</v>
+        <v>1125</v>
       </c>
       <c r="C23" s="35" t="s">
         <v>41</v>
@@ -1627,7 +1639,7 @@
       </c>
       <c r="B24" s="36">
         <f>CEILING(IF(ISNUMBER(B11), B11, B12), 0.1)</f>
-        <v>4456</v>
+        <v>1362.5</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>43</v>
@@ -1661,7 +1673,7 @@
       </c>
       <c r="B25" s="36">
         <f>CEILING(B12 - B15, 0.1)</f>
-        <v>4445</v>
+        <v>1354.5</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>45</v>
@@ -1695,9 +1707,11 @@
       </c>
       <c r="B26" s="36">
         <f>CEILING(B24+B8*B15, 0.25)</f>
-        <v>4489</v>
+        <v>1386.5</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="35" t="s">
+        <v>47</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
@@ -1721,16 +1735,16 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
     </row>
-    <row r="27" ht="36.0" customHeight="1">
+    <row r="27" ht="68.25" customHeight="1">
       <c r="A27" s="33" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="37">
-        <f>ROUND((B24-B25)*B23,0)</f>
-        <v>5005</v>
+        <f>B24+B15*B8*2</f>
+        <v>1410.5</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1755,15 +1769,17 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28" ht="42.75" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>49</v>
+    <row r="28" ht="36.0" customHeight="1">
+      <c r="A28" s="33" t="s">
+        <v>50</v>
       </c>
-      <c r="B28" s="38">
-        <f>ROUND((B26-B24)*B23,0)</f>
-        <v>15015</v>
+      <c r="B28" s="37">
+        <f>ROUND((B24-B25)*B23,0)</f>
+        <v>9000</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="35" t="s">
+        <v>51</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1787,10 +1803,15 @@
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
     </row>
-    <row r="29" ht="21.75" customHeight="1">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="39"/>
+    <row r="29" ht="42.75" customHeight="1">
+      <c r="A29" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="38">
+        <f>ROUND((B26-B24)*B23,0)</f>
+        <v>27000</v>
+      </c>
+      <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -1922,7 +1943,7 @@
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="21.75" customHeight="1">
       <c r="A34" s="39"/>
       <c r="B34" s="40"/>
       <c r="C34" s="39"/>
@@ -28004,6 +28025,33 @@
       <c r="X999" s="4"/>
       <c r="Y999" s="4"/>
     </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="A1000" s="39"/>
+      <c r="B1000" s="40"/>
+      <c r="C1000" s="39"/>
+      <c r="D1000" s="4"/>
+      <c r="E1000" s="4"/>
+      <c r="F1000" s="4"/>
+      <c r="G1000" s="4"/>
+      <c r="H1000" s="4"/>
+      <c r="I1000" s="4"/>
+      <c r="J1000" s="4"/>
+      <c r="K1000" s="4"/>
+      <c r="L1000" s="4"/>
+      <c r="M1000" s="4"/>
+      <c r="N1000" s="4"/>
+      <c r="O1000" s="4"/>
+      <c r="P1000" s="4"/>
+      <c r="Q1000" s="4"/>
+      <c r="R1000" s="4"/>
+      <c r="S1000" s="4"/>
+      <c r="T1000" s="4"/>
+      <c r="U1000" s="4"/>
+      <c r="V1000" s="4"/>
+      <c r="W1000" s="4"/>
+      <c r="X1000" s="4"/>
+      <c r="Y1000" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <r>
       <rPr>
@@ -104,10 +104,16 @@
     <t>ATR multiple for stop distance</t>
   </si>
   <si>
-    <t>Target Multiplier</t>
+    <t>Fixed Target Multiplier</t>
   </si>
   <si>
     <t>3R</t>
+  </si>
+  <si>
+    <t>Dynamic Target Multiplier</t>
+  </si>
+  <si>
+    <t>10R</t>
   </si>
   <si>
     <t>TRADE INPUTS</t>
@@ -145,7 +151,7 @@
     <t>AVALON</t>
   </si>
   <si>
-    <t>Mandatory Input Field (Not case-sensitive)</t>
+    <t>Mandatory Input Field (Not case-sensitive). It will convert to UPPER automatically</t>
   </si>
   <si>
     <r>
@@ -327,28 +333,37 @@
     <t>SL price may vary slightly due to slippage when using a Stop-Loss Market (SL-M) order.</t>
   </si>
   <si>
-    <t>Target Price (T1)</t>
+    <t>Target Price ( T1 )</t>
   </si>
   <si>
     <t xml:space="preserve">The primary target — and in most cases, the only target that matters.
 </t>
   </si>
   <si>
-    <t>Target Price (T2)</t>
+    <t>Target Price ( T2 )</t>
   </si>
   <si>
-    <t xml:space="preserve">The secondary target should only be used if you plan to follow a dynamic exit strategy — for example, booking 50% at T1, moving the stop loss to breakeven, and then trailing the remaining position below each new swing low until T2 is hit.
+    <t xml:space="preserve">The secondary target should only be used if you plan to follow a dynamic exit strategy — for example, booking 60% at T1, moving the stop loss to breakeven, and then trailing the remaining position below each new swing low until T2 is hit.
 This approach is not perfect. Some days, price will reverse after hitting T1, reducing your overall profit. On other days, the move will continue to T2 and deliver larger gains. Be prepared mentally for both outcomes.
 </t>
   </si>
   <si>
-    <t>Loss Amount</t>
+    <t>Quantity ( Q1 )</t>
+  </si>
+  <si>
+    <t>60% of total quantity to exit at T1. This must be only used in dynamic exit strategy</t>
+  </si>
+  <si>
+    <t>Quantity ( Q2 )</t>
+  </si>
+  <si>
+    <t>Remaining quantity to exit at T2. This must be only used in dynamic exit strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R </t>
   </si>
   <si>
     <t>Loss amount may vary slightly due to SL slippage</t>
-  </si>
-  <si>
-    <t>Profit Amount</t>
   </si>
 </sst>
 </file>
@@ -655,8 +670,8 @@
     <xf borderId="4" fillId="12" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="12" fontId="12" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="12" fontId="12" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -881,7 +896,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="32.0"/>
+    <col customWidth="1" min="1" max="1" width="44.71"/>
     <col customWidth="1" min="2" max="2" width="18.0"/>
     <col customWidth="1" min="3" max="3" width="121.14"/>
     <col customWidth="1" min="4" max="25" width="8.71"/>
@@ -1143,12 +1158,16 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
     </row>
-    <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="5" t="s">
+    <row r="9" ht="21.75" customHeight="1">
+      <c r="A9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
+      <c r="B9" s="17">
+        <v>10.0</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>16</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1172,16 +1191,12 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
     </row>
-    <row r="10" ht="35.25" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="20" t="s">
+    <row r="10" ht="15.0" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="3"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1205,12 +1220,12 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
     </row>
-    <row r="11" ht="46.5" customHeight="1">
+    <row r="11" ht="35.25" customHeight="1">
       <c r="A11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>19</v>
-      </c>
-      <c r="B11" s="20">
-        <v>1362.5</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>20</v>
@@ -1239,14 +1254,13 @@
       <c r="Y11" s="4"/>
     </row>
     <row r="12" ht="46.5" customHeight="1">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="22">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(ISNUMBER(B11), B11, GOOGLEFINANCE(""NSE:""&amp;B10,""high""))"),1362.5)</f>
+      <c r="B12" s="20">
         <v>1362.5</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="18" t="s">
         <v>22</v>
       </c>
       <c r="D12" s="4"/>
@@ -1272,12 +1286,13 @@
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
     </row>
-    <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="23" t="s">
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="A13" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="24">
-        <v>16.0</v>
+      <c r="B13" s="22">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IF(ISNUMBER(B12), B12, GOOGLEFINANCE(""NSE:""&amp;B11,""high""))"),1362.5)</f>
+        <v>1362.5</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>24</v>
@@ -1305,12 +1320,16 @@
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
     </row>
-    <row r="14" ht="21.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+    <row r="14" ht="36.75" customHeight="1">
+      <c r="A14" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
+      <c r="B14" s="24">
+        <v>16.0</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>26</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1335,16 +1354,11 @@
       <c r="Y14" s="4"/>
     </row>
     <row r="15" ht="21.75" customHeight="1">
-      <c r="A15" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="25">
-        <f>CEILING(B13*B7, 0.1)</f>
-        <v>8</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="A15" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1368,15 +1382,15 @@
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
     </row>
-    <row r="16" ht="33.0" customHeight="1">
+    <row r="16" ht="21.75" customHeight="1">
       <c r="A16" s="21" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="25">
-        <f>B4*B5</f>
-        <v>9000</v>
+        <f>CEILING(B14*B7, 0.1)</f>
+        <v>8</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="26" t="s">
         <v>29</v>
       </c>
       <c r="D16" s="4"/>
@@ -1402,15 +1416,15 @@
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
     </row>
-    <row r="17" ht="21.75" customHeight="1">
-      <c r="A17" s="11" t="s">
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="21" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="25">
-        <f>B4*B6</f>
-        <v>2025000</v>
+        <f>B4*B5</f>
+        <v>9000</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="4"/>
@@ -1440,9 +1454,9 @@
       <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="28">
-        <f>IF(B15&gt;0,B16/B15,0)</f>
-        <v>1125</v>
+      <c r="B18" s="25">
+        <f>B4*B6</f>
+        <v>2025000</v>
       </c>
       <c r="C18" s="26" t="s">
         <v>33</v>
@@ -1474,9 +1488,9 @@
       <c r="A19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="29">
-        <f>B17/B12</f>
-        <v>1486.238532</v>
+      <c r="B19" s="28">
+        <f>IF(B16&gt;0,B17/B16,0)</f>
+        <v>1125</v>
       </c>
       <c r="C19" s="26" t="s">
         <v>35</v>
@@ -1505,12 +1519,12 @@
       <c r="Y19" s="4"/>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="11" t="s">
         <v>36</v>
       </c>
       <c r="B20" s="29">
-        <f>MIN(B18,B19)</f>
-        <v>1125</v>
+        <f>B18/B13</f>
+        <v>1486.238532</v>
       </c>
       <c r="C20" s="26" t="s">
         <v>37</v>
@@ -1538,12 +1552,17 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
     </row>
-    <row r="21" ht="24.0" customHeight="1">
-      <c r="A21" s="30" t="s">
+    <row r="21" ht="21.75" customHeight="1">
+      <c r="A21" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
+      <c r="B21" s="29">
+        <f>MIN(B19,B20)</f>
+        <v>1125</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>39</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1567,15 +1586,12 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
     </row>
-    <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>39</v>
+    <row r="22" ht="24.0" customHeight="1">
+      <c r="A22" s="30" t="s">
+        <v>40</v>
       </c>
-      <c r="B22" s="32" t="str">
-        <f>B10</f>
-        <v>AVALON</v>
-      </c>
-      <c r="C22" s="4"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="3"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
@@ -1599,17 +1615,15 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
     </row>
-    <row r="23" ht="35.25" customHeight="1">
-      <c r="A23" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="34">
-        <f>IF(B20&gt;5, ROUND(B20/5, 0)*5, B20)</f>
-        <v>1125</v>
-      </c>
-      <c r="C23" s="35" t="s">
+    <row r="23" ht="30.75" customHeight="1">
+      <c r="A23" s="31" t="s">
         <v>41</v>
       </c>
+      <c r="B23" s="32" t="str">
+        <f>B11</f>
+        <v>AVALON</v>
+      </c>
+      <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -1633,13 +1647,13 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
     </row>
-    <row r="24" ht="37.5" customHeight="1">
+    <row r="24" ht="35.25" customHeight="1">
       <c r="A24" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="36">
-        <f>CEILING(IF(ISNUMBER(B11), B11, B12), 0.1)</f>
-        <v>1362.5</v>
+      <c r="B24" s="34">
+        <f>IF(B21&gt;5, ROUND(B21/5, 0)*5, B21)</f>
+        <v>1125</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>43</v>
@@ -1667,13 +1681,13 @@
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
     </row>
-    <row r="25" ht="34.5" customHeight="1">
+    <row r="25" ht="37.5" customHeight="1">
       <c r="A25" s="33" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="36">
-        <f>CEILING(B12 - B15, 0.1)</f>
-        <v>1354.5</v>
+        <f>CEILING(IF(ISNUMBER(B12), B12, B13), 0.1)</f>
+        <v>1362.5</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>45</v>
@@ -1701,13 +1715,13 @@
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
     </row>
-    <row r="26" ht="39.75" customHeight="1">
+    <row r="26" ht="34.5" customHeight="1">
       <c r="A26" s="33" t="s">
         <v>46</v>
       </c>
       <c r="B26" s="36">
-        <f>CEILING(B24+B8*B15, 0.25)</f>
-        <v>1386.5</v>
+        <f>CEILING(B13 - B16, 0.1)</f>
+        <v>1354.5</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>47</v>
@@ -1735,13 +1749,13 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
     </row>
-    <row r="27" ht="68.25" customHeight="1">
+    <row r="27" ht="39.75" customHeight="1">
       <c r="A27" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="37">
-        <f>B24+B15*B8*2</f>
-        <v>1410.5</v>
+      <c r="B27" s="36">
+        <f>CEILING(B25+B8*B16, 0.25)</f>
+        <v>1386.5</v>
       </c>
       <c r="C27" s="35" t="s">
         <v>49</v>
@@ -1769,13 +1783,13 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28" ht="36.0" customHeight="1">
+    <row r="28" ht="68.25" customHeight="1">
       <c r="A28" s="33" t="s">
         <v>50</v>
       </c>
       <c r="B28" s="37">
-        <f>ROUND((B24-B25)*B23,0)</f>
-        <v>9000</v>
+        <f>B25+B16*B9</f>
+        <v>1442.5</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>51</v>
@@ -1803,15 +1817,17 @@
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
     </row>
-    <row r="29" ht="42.75" customHeight="1">
-      <c r="A29" s="31" t="s">
+    <row r="29" ht="36.0" customHeight="1">
+      <c r="A29" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B29" s="38">
-        <f>ROUND((B26-B24)*B23,0)</f>
-        <v>27000</v>
+        <f>round(0.6*B24,0)</f>
+        <v>675</v>
       </c>
-      <c r="C29" s="4"/>
+      <c r="C29" s="35" t="s">
+        <v>53</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -1835,10 +1851,17 @@
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
     </row>
-    <row r="30" ht="21.75" customHeight="1">
-      <c r="A30" s="39"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="39"/>
+    <row r="30" ht="36.0" customHeight="1">
+      <c r="A30" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B30" s="38">
+        <f>B24-B29</f>
+        <v>450</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>55</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1862,10 +1885,17 @@
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
     </row>
-    <row r="31" ht="21.75" customHeight="1">
-      <c r="A31" s="39"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="39"/>
+    <row r="31" ht="36.0" customHeight="1">
+      <c r="A31" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="37">
+        <f>ROUND((B25-B26)*B24,0)</f>
+        <v>9000</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -1970,7 +2000,7 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="21.75" customHeight="1">
       <c r="A35" s="39"/>
       <c r="B35" s="40"/>
       <c r="C35" s="39"/>
@@ -28052,13 +28082,40 @@
       <c r="X1000" s="4"/>
       <c r="Y1000" s="4"/>
     </row>
+    <row r="1001" ht="15.75" customHeight="1">
+      <c r="A1001" s="39"/>
+      <c r="B1001" s="40"/>
+      <c r="C1001" s="39"/>
+      <c r="D1001" s="4"/>
+      <c r="E1001" s="4"/>
+      <c r="F1001" s="4"/>
+      <c r="G1001" s="4"/>
+      <c r="H1001" s="4"/>
+      <c r="I1001" s="4"/>
+      <c r="J1001" s="4"/>
+      <c r="K1001" s="4"/>
+      <c r="L1001" s="4"/>
+      <c r="M1001" s="4"/>
+      <c r="N1001" s="4"/>
+      <c r="O1001" s="4"/>
+      <c r="P1001" s="4"/>
+      <c r="Q1001" s="4"/>
+      <c r="R1001" s="4"/>
+      <c r="S1001" s="4"/>
+      <c r="T1001" s="4"/>
+      <c r="U1001" s="4"/>
+      <c r="V1001" s="4"/>
+      <c r="W1001" s="4"/>
+      <c r="X1001" s="4"/>
+      <c r="Y1001" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A22:C22"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -126,7 +126,7 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>ENRIN</t>
+    <t>PANACEABIO</t>
   </si>
   <si>
     <t>Mandatory Input Field (Not case-sensitive). It will convert to UPPER automatically</t>
@@ -135,7 +135,7 @@
     <t>* Trade Type</t>
   </si>
   <si>
-    <t>Long</t>
+    <t>Short</t>
   </si>
   <si>
     <t>Mandatory Input Field. Enter high of confirmation candle</t>
@@ -1634,10 +1634,10 @@
     <row r="16" ht="46.5" customHeight="1">
       <c r="A16" s="36" t="str">
         <f>IF(B15="Long", "*  Confirmation High", "*  Confirmation Low")</f>
-        <v>*  Confirmation High</v>
+        <v>*  Confirmation Low</v>
       </c>
       <c r="B16" s="37">
-        <v>3725.0</v>
+        <v>552.95</v>
       </c>
       <c r="C16" s="38" t="s">
         <v>29</v>
@@ -1671,7 +1671,7 @@
         <v>30</v>
       </c>
       <c r="B17" s="40">
-        <v>13.55</v>
+        <v>5.57</v>
       </c>
       <c r="C17" s="14" t="s">
         <v>31</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B18" s="42">
         <f>B17/B16</f>
-        <v>0.003637583893</v>
+        <v>0.01007324351</v>
       </c>
       <c r="C18" s="43" t="s">
         <v>33</v>
@@ -1740,7 +1740,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="44">
-        <v>1.8</v>
+        <v>0.25</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="7"/>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B20" s="45">
         <f>IF(ISNUMBER(B16), IF(B15="Long", B16 + B17*B10, B16 - B17*B10), 0)</f>
-        <v>3725.6775</v>
+        <v>552.6715</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>36</v>
@@ -1811,7 +1811,7 @@
    ),
    ""
 )</f>
-        <v>⚠️ WARNING: Spread exceeds limit — position sizing blocked. Avoid this trade due to high slippage risk.</v>
+        <v/>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B23" s="47">
         <f>CEILING(B17*B7, 0.1)</f>
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="C23" s="48" t="s">
         <v>39</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B26" s="49">
         <f>IF(B23&gt;0,B24/B23,0)</f>
-        <v>1470.588235</v>
+        <v>3571.428571</v>
       </c>
       <c r="C26" s="48" t="s">
         <v>45</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="B27" s="49">
         <f>IF(B20&gt;0, B25/B20, 0)</f>
-        <v>603.9170057</v>
+        <v>4071.13448</v>
       </c>
       <c r="C27" s="48" t="s">
         <v>47</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B28" s="49">
         <f>MIN(B26,B27)</f>
-        <v>603.9170057</v>
+        <v>3571.428571</v>
       </c>
       <c r="C28" s="48" t="s">
         <v>49</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B30" s="52" t="str">
         <f>B14</f>
-        <v>ENRIN</v>
+        <v>PANACEABIO</v>
       </c>
       <c r="C30" s="53"/>
       <c r="D30" s="7"/>
@@ -2146,9 +2146,9 @@
       <c r="A31" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="B31" s="55" t="str">
+      <c r="B31" s="55">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B28&gt;5, ROUND(B28/5, 0)*5, B28))</f>
-        <v>⚠️ N/A</v>
+        <v>3570</v>
       </c>
       <c r="C31" s="53" t="s">
         <v>53</v>
@@ -2181,9 +2181,9 @@
       <c r="A32" s="54" t="s">
         <v>54</v>
       </c>
-      <c r="B32" s="56" t="str">
+      <c r="B32" s="56">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",B20)</f>
-        <v>⚠️ N/A</v>
+        <v>552.6715</v>
       </c>
       <c r="C32" s="53" t="s">
         <v>55</v>
@@ -2216,9 +2216,9 @@
       <c r="A33" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="56" t="str">
+      <c r="B33" s="56">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B15="Long",CEILING(B20 - B23, 0.1),CEILING(B20 + B23, 0.1)))</f>
-        <v>⚠️ N/A</v>
+        <v>555.5</v>
       </c>
       <c r="C33" s="53" t="s">
         <v>57</v>
@@ -2251,9 +2251,9 @@
       <c r="A34" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="B34" s="56" t="str">
+      <c r="B34" s="56">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B15="Long",CEILING(B32+B8*B23, 0.25),CEILING(B32-B8*B23, 0.25)))</f>
-        <v>⚠️ N/A</v>
+        <v>543</v>
       </c>
       <c r="C34" s="53" t="s">
         <v>59</v>
@@ -2286,9 +2286,9 @@
       <c r="A35" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="56" t="str">
+      <c r="B35" s="56">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B15="Long",CEILING(B32+B23*B9, 0.25),CEILING(B32-B23*B9, 0.25)))</f>
-        <v>⚠️ N/A</v>
+        <v>530.5</v>
       </c>
       <c r="C35" s="53" t="s">
         <v>61</v>
@@ -2321,9 +2321,9 @@
       <c r="A36" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="55" t="str">
+      <c r="B36" s="55">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",ROUND(B12*B31,0))</f>
-        <v>⚠️ N/A</v>
+        <v>1785</v>
       </c>
       <c r="C36" s="53" t="s">
         <v>63</v>
@@ -2356,9 +2356,9 @@
       <c r="A37" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="55" t="str">
+      <c r="B37" s="55">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",B31-B36)</f>
-        <v>⚠️ N/A</v>
+        <v>1785</v>
       </c>
       <c r="C37" s="53" t="s">
         <v>65</v>
@@ -2391,9 +2391,9 @@
       <c r="A38" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="B38" s="57" t="str">
+      <c r="B38" s="57">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B15="Long",ROUND((B32-B33)*B31,0),ROUND((B33-B32)*B31,0)))</f>
-        <v>⚠️ N/A</v>
+        <v>10098</v>
       </c>
       <c r="C38" s="53" t="s">
         <v>67</v>
@@ -2426,9 +2426,9 @@
       <c r="A39" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="58" t="str">
+      <c r="B39" s="58">
         <f>IF(AND(B17&gt;0,B19&gt;0,B19/B17&gt;=B11),"⚠️ N/A",IF(B15="Long",(B34-B32)*B31,(B32-B34)*B31))</f>
-        <v>⚠️ N/A</v>
+        <v>34527.255</v>
       </c>
       <c r="C39" s="53" t="s">
         <v>69</v>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -139,7 +139,7 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>FINCABLES</t>
+    <t>LGEINDIA</t>
   </si>
   <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
@@ -148,7 +148,7 @@
     <t>*  Trade Type</t>
   </si>
   <si>
-    <t>Short</t>
+    <t>Long</t>
   </si>
   <si>
     <t>Trade Direction: Select LONG or SHORT. SL and target prices are computed accordingly.</t>
@@ -157,7 +157,7 @@
     <t>*  Setup</t>
   </si>
   <si>
-    <t>NSE Topers</t>
+    <t>EVB</t>
   </si>
   <si>
     <t>Select Setup: Different setups use different target values based on backtesting.</t>
@@ -185,7 +185,7 @@
     <t>*  Entry</t>
   </si>
   <si>
-    <t>Breakout Candle</t>
+    <t>Confirmation Candle</t>
   </si>
   <si>
     <t>Are you entering at the confirmation candle, or at the breakout candle</t>
@@ -211,7 +211,7 @@
         <rFont val="Calibri"/>
         <color rgb="FF595959"/>
       </rPr>
-      <t xml:space="preserve">Participation Filter - Measure participation on the 3-minute timeframe after entry. 
+      <t xml:space="preserve">Participation Filter - Measure participation on the 2-minute timeframe after entry. 
 </t>
     </r>
     <r>
@@ -1794,13 +1794,13 @@
 B19="EVB",2/B7
 )
 +IF(B27="Strong",1/B7,0)
-+IF(B26="Market",0.25,0),
++IF(B26="Market",0.5,0),
 0.25)</f>
-        <v>6.25</v>
+        <v>4.5</v>
       </c>
       <c r="C8" s="24" t="str">
         <f t="shared" ref="C8:C9" si="1">B8 &amp; "R"</f>
-        <v>6.25R</v>
+        <v>4.5R</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1833,11 +1833,11 @@
       <c r="B9" s="28">
         <f>CEILING(B8*2.5,1)
  </f>
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>16R</v>
+        <v>12R</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -2004,7 +2004,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="38">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="7"/>
@@ -2199,10 +2199,10 @@
     <row r="20" ht="46.5" customHeight="1">
       <c r="A20" s="45" t="str">
         <f>IF(B18="Long", "*  Breakout High", "*  Breakout Low")</f>
-        <v>*  Breakout Low</v>
+        <v>*  Breakout High</v>
       </c>
       <c r="B20" s="46">
-        <v>1317.75</v>
+        <v>1653.2</v>
       </c>
       <c r="C20" s="48" t="s">
         <v>35</v>
@@ -2234,10 +2234,10 @@
     <row r="21" ht="46.5" customHeight="1">
       <c r="A21" s="49" t="str">
         <f>IF(B18="Long", "*  Confirmation High", "*  Confirmation Low")</f>
-        <v>*  Confirmation Low</v>
+        <v>*  Confirmation High</v>
       </c>
       <c r="B21" s="50">
-        <v>1306.1</v>
+        <v>1642.4</v>
       </c>
       <c r="C21" s="48" t="s">
         <v>36</v>
@@ -2271,7 +2271,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="52">
-        <v>23.0</v>
+        <v>8.58</v>
       </c>
       <c r="C22" s="18" t="s">
         <v>38</v>
@@ -2305,7 +2305,7 @@
         <v>39</v>
       </c>
       <c r="B23" s="54">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="7"/>
@@ -2335,10 +2335,10 @@
     <row r="24" ht="52.5" customHeight="1">
       <c r="A24" s="53" t="str">
         <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
-        <v>* Lower Circuit</v>
+        <v>* Upper Circuit</v>
       </c>
       <c r="B24" s="54">
-        <v>966.0</v>
+        <v>1736.1</v>
       </c>
       <c r="C24" s="55" t="s">
         <v>40</v>
@@ -2469,13 +2469,13 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28" ht="46.5" customHeight="1">
+    <row r="28" ht="46.5" hidden="1" customHeight="1">
       <c r="A28" s="58" t="s">
         <v>50</v>
       </c>
       <c r="B28" s="59">
         <f>IF(AND(B22&gt;0, B23&gt;0), B23/B22,0)</f>
-        <v>0.02608695652</v>
+        <v>0.0641025641</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="7"/>
@@ -2502,7 +2502,7 @@
       <c r="Y28" s="7"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" ht="46.5" customHeight="1">
+    <row r="29" ht="46.5" hidden="1" customHeight="1">
       <c r="A29" s="58" t="s">
         <v>51</v>
       </c>
@@ -2539,13 +2539,13 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" ht="46.5" customHeight="1">
+    <row r="30" ht="46.5" hidden="1" customHeight="1">
       <c r="A30" s="61" t="s">
         <v>52</v>
       </c>
       <c r="B30" s="62">
         <f>IF(B25="Confirmation Candle",B21, B20)</f>
-        <v>1317.75</v>
+        <v>1642.4</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="7"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B32" s="63">
         <f>FLOOR(B22*B7, 0.1)</f>
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>55</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B35" s="64">
         <f>IF(B32&gt;0,B33/B32,0)</f>
-        <v>1086.956522</v>
+        <v>2976.190476</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>61</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B36" s="64">
         <f>IF(B30&gt;0, B34/B30, 0)</f>
-        <v>1802.314551</v>
+        <v>1446.054554</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>63</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B37" s="65">
         <f>MIN(B35,B36)</f>
-        <v>1086.956522</v>
+        <v>1446.054554</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>65</v>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="B42" s="75" t="str">
         <f>B17</f>
-        <v>FINCABLES</v>
+        <v>LGEINDIA</v>
       </c>
       <c r="C42" s="76"/>
       <c r="D42" s="7"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="B43" s="78">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B37&gt;5, ROUND(B37/5, 0)*5, B37))</f>
-        <v>1085</v>
+        <v>1445</v>
       </c>
       <c r="C43" s="79" t="s">
         <v>71</v>
@@ -3024,7 +3024,7 @@
     B18="Long", B30+B10*B29,
     B18="Short", B30-B10*B29
 )</f>
-        <v>1317.55</v>
+        <v>1642.6</v>
       </c>
       <c r="C44" s="79" t="s">
         <v>73</v>
@@ -3102,7 +3102,7 @@
     "⚠️ N/A"
   )
 )</f>
-        <v>1337.1</v>
+        <v>1635.4</v>
       </c>
       <c r="C46" s="82" t="s">
         <v>76</v>
@@ -3148,7 +3148,7 @@
     )
   )
 )</f>
-        <v>1329.1</v>
+        <v>1638.4</v>
       </c>
       <c r="C47" s="79" t="s">
         <v>78</v>
@@ -3194,7 +3194,7 @@
     )
   )
 )</f>
-        <v>1245.6</v>
+        <v>1661.5</v>
       </c>
       <c r="C48" s="79" t="s">
         <v>80</v>
@@ -3240,7 +3240,7 @@
     )
   )
 )</f>
-        <v>1133.5</v>
+        <v>1693</v>
       </c>
       <c r="C49" s="82" t="s">
         <v>82</v>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="B50" s="78">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",ROUND(B12*B43,0))</f>
-        <v>434</v>
+        <v>578</v>
       </c>
       <c r="C50" s="82" t="s">
         <v>84</v>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B51" s="78">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",B43-B50)</f>
-        <v>651</v>
+        <v>867</v>
       </c>
       <c r="C51" s="82" t="s">
         <v>86</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="B52" s="83">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",ROUND((B44-B47)*B43,0),ROUND((B47-B44)*B43,0)))</f>
-        <v>12532</v>
+        <v>6069</v>
       </c>
       <c r="C52" s="79" t="s">
         <v>88</v>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B53" s="84" t="str">
         <f>ROUND(B52/B15,1) &amp; "R"</f>
-        <v>1R</v>
+        <v>0.5R</v>
       </c>
       <c r="C53" s="82" t="s">
         <v>90</v>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="B54" s="86">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B19="Long",ROUND((B46-B44)*B43,0),ROUND((B46-B44)*B43,0)))</f>
-        <v>21212</v>
+        <v>-10404</v>
       </c>
       <c r="C54" s="82" t="s">
         <v>92</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="B55" s="88" t="str">
         <f>ROUND(B54/B15,1) &amp; "R"</f>
-        <v>1.7R</v>
+        <v>-0.8R</v>
       </c>
       <c r="C55" s="89" t="s">
         <v>94</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="B56" s="90">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",(B48-B44)*B43,(B44-B48)*B43))</f>
-        <v>78065.75</v>
+        <v>27310.5</v>
       </c>
       <c r="C56" s="91" t="s">
         <v>96</v>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B57" s="92" t="str">
         <f>ROUND(B56/B15,1) &amp; "R"</f>
-        <v>6.2R</v>
+        <v>2.2R</v>
       </c>
       <c r="C57" s="89" t="s">
         <v>98</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="B58" s="90">
         <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",(B48-B44)*B50+(B49-B44)*B51,(B44-B48)*B50+(B44-B49)*B51))</f>
-        <v>151042.85</v>
+        <v>54621</v>
       </c>
       <c r="C58" s="89" t="s">
         <v>100</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B59" s="94" t="str">
         <f>ROUND(B58/B15,1) &amp; "R"</f>
-        <v>12.1R</v>
+        <v>4.4R</v>
       </c>
       <c r="C59" s="95" t="s">
         <v>102</v>
@@ -30449,8 +30449,8 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
   </mergeCells>
   <conditionalFormatting sqref="B44">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -16,6 +16,13 @@
     <author/>
   </authors>
   <commentList>
+    <comment authorId="0" ref="B50">
+      <text>
+        <t xml:space="preserve">Legend
+🟠 Orange – SELL
+🔵 Blue – BUY</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="B49">
       <text>
         <t xml:space="preserve">Legend
@@ -37,14 +44,7 @@
 🔵 Blue – BUY</t>
       </text>
     </comment>
-    <comment authorId="0" ref="B46">
-      <text>
-        <t xml:space="preserve">Legend
-🟠 Orange – SELL
-🔵 Blue – BUY</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B44">
+    <comment authorId="0" ref="B45">
       <text>
         <t xml:space="preserve">Legend
 🟠 Orange – SELL
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>📊  Position Size Calculator ( Fill in the required fields marked with * )</t>
   </si>
@@ -139,7 +139,7 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>LGEINDIA</t>
+    <t>AVANTIFEED</t>
   </si>
   <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>Min of risk-based vs capital-based</t>
+  </si>
+  <si>
+    <t>Is Wide Spread</t>
   </si>
   <si>
     <t>T1 Near Circuit?</t>
@@ -1153,7 +1156,7 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1549,7 +1552,9 @@
     <col customWidth="1" min="1" max="1" width="35.29"/>
     <col customWidth="1" min="2" max="2" width="26.71"/>
     <col customWidth="1" min="3" max="3" width="121.14"/>
-    <col customWidth="1" min="4" max="23" width="8.71"/>
+    <col customWidth="1" min="4" max="5" width="8.71"/>
+    <col customWidth="1" min="6" max="6" width="16.14"/>
+    <col customWidth="1" min="7" max="23" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="36.0" customHeight="1">
@@ -2004,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="B14" s="38">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="7"/>
@@ -2201,9 +2206,7 @@
         <f>IF(B18="Long", "*  Breakout High", "*  Breakout Low")</f>
         <v>*  Breakout High</v>
       </c>
-      <c r="B20" s="46">
-        <v>1653.2</v>
-      </c>
+      <c r="B20" s="46"/>
       <c r="C20" s="48" t="s">
         <v>35</v>
       </c>
@@ -2236,9 +2239,7 @@
         <f>IF(B18="Long", "*  Confirmation High", "*  Confirmation Low")</f>
         <v>*  Confirmation High</v>
       </c>
-      <c r="B21" s="50">
-        <v>1642.4</v>
-      </c>
+      <c r="B21" s="50"/>
       <c r="C21" s="48" t="s">
         <v>36</v>
       </c>
@@ -2270,9 +2271,7 @@
       <c r="A22" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="52">
-        <v>8.58</v>
-      </c>
+      <c r="B22" s="52"/>
       <c r="C22" s="18" t="s">
         <v>38</v>
       </c>
@@ -2304,9 +2303,7 @@
       <c r="A23" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="54">
-        <v>0.55</v>
-      </c>
+      <c r="B23" s="54"/>
       <c r="C23" s="14"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -2337,9 +2334,7 @@
         <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
         <v>* Upper Circuit</v>
       </c>
-      <c r="B24" s="54">
-        <v>1736.1</v>
-      </c>
+      <c r="B24" s="54"/>
       <c r="C24" s="55" t="s">
         <v>40</v>
       </c>
@@ -2475,7 +2470,7 @@
       </c>
       <c r="B28" s="59">
         <f>IF(AND(B22&gt;0, B23&gt;0), B23/B22,0)</f>
-        <v>0.0641025641</v>
+        <v>0</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="7"/>
@@ -2507,12 +2502,13 @@
         <v>51</v>
       </c>
       <c r="B29" s="60">
-        <f>IF(B21&lt;250,0.01,
+        <f>IF(B21&lt;1,0,
+ IF(B21&lt;250,0.01,
  IF(B21&lt;=1000,0.05,
  IF(B21&lt;=5000,0.1,
  IF(B21&lt;=10000,0.5,
- IF(B21&lt;=20000,1,5)))))</f>
-        <v>0.1</v>
+ IF(B21&lt;=20000,1,5))))))</f>
+        <v>0</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="7"/>
@@ -2544,8 +2540,8 @@
         <v>52</v>
       </c>
       <c r="B30" s="62">
-        <f>IF(B25="Confirmation Candle",B21, B20)</f>
-        <v>1642.4</v>
+        <f>LET(x,IF(B25="Confirmation Candle",B21,B20),IF(ISNUMBER(x),x,0))</f>
+        <v>0</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="7"/>
@@ -2608,7 +2604,7 @@
       </c>
       <c r="B32" s="63">
         <f>FLOOR(B22*B7, 0.1)</f>
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="C32" s="14" t="s">
         <v>55</v>
@@ -2713,7 +2709,7 @@
       </c>
       <c r="B35" s="64">
         <f>IF(B32&gt;0,B33/B32,0)</f>
-        <v>2976.190476</v>
+        <v>0</v>
       </c>
       <c r="C35" s="14" t="s">
         <v>61</v>
@@ -2748,7 +2744,7 @@
       </c>
       <c r="B36" s="64">
         <f>IF(B30&gt;0, B34/B30, 0)</f>
-        <v>1446.054554</v>
+        <v>0</v>
       </c>
       <c r="C36" s="14" t="s">
         <v>63</v>
@@ -2783,7 +2779,7 @@
       </c>
       <c r="B37" s="65">
         <f>MIN(B35,B36)</f>
-        <v>1446.054554</v>
+        <v>0</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>65</v>
@@ -2817,7 +2813,7 @@
         <v>66</v>
       </c>
       <c r="B38" s="67" t="b">
-        <f>AND(B48&lt;B24,(B24-B48)/B24&lt;=B14)</f>
+        <f>B28&gt;B11</f>
         <v>0</v>
       </c>
       <c r="C38" s="68"/>
@@ -2850,7 +2846,7 @@
         <v>67</v>
       </c>
       <c r="B39" s="67" t="b">
-        <f>AND(B49&lt;B24,(B24-B49)/B24&lt;=B14)</f>
+        <f>IF(B24&lt;1,FALSE,(B24-B49)/B24&lt;=B14)</f>
         <v>0</v>
       </c>
       <c r="C39" s="68"/>
@@ -2878,24 +2874,19 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="8"/>
     </row>
-    <row r="40" ht="47.25" customHeight="1">
-      <c r="A40" s="69" t="str">
-        <f>IF(AND(B28&gt;0,B28&gt;=B11),
-   "⚠️ WARNING: Spread exceeds limit — position sizing blocked. Avoid this trade due to high slippage risk.",
-   IF(B38,
-      "☠️ WARNING: First Target (T1) is near the circuit limit — DO NOT TRADE",
-      IF(B39,
-         "⚠️ WARNING: Second Target (T2) is near the circuit limit — EXIT 100% at T1",
-         ""
-      )
-   )
-)</f>
-        <v/>
+    <row r="40" ht="21.75" hidden="1" customHeight="1">
+      <c r="A40" s="66" t="s">
+        <v>68</v>
       </c>
+      <c r="B40" s="67" t="b">
+        <f>IF(B24&lt;1,FALSE,(B24-B50)/B24&lt;=B14)</f>
+        <v>0</v>
+      </c>
+      <c r="C40" s="68"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="70"/>
+      <c r="G40" s="7"/>
       <c r="H40" s="7"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
@@ -2916,16 +2907,28 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="8"/>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
-      <c r="A41" s="71" t="s">
-        <v>68</v>
+    <row r="41" ht="63.0" customHeight="1">
+      <c r="A41" s="69" t="str">
+        <f>IFERROR(
+   IF(B38,
+      "☠️ Spread Too High — High Slippage Risk - DO NOT TRADE",
+      IF(B39,
+         "☠️ T1 near circuit limit — False Breakout / Reversal Risk - DO NOT TRADE",
+         IF(B40,
+            "☠️ T2 near circuit limit — Exit 100% at T1",
+            ""
+         )
+      )
+   ),
+   ""
+)
+</f>
+        <v/>
       </c>
-      <c r="B41" s="72"/>
-      <c r="C41" s="73"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
+      <c r="G41" s="70"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
@@ -2946,15 +2949,12 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="8"/>
     </row>
-    <row r="42" ht="30.75" customHeight="1">
-      <c r="A42" s="74" t="s">
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="75" t="str">
-        <f>B17</f>
-        <v>LGEINDIA</v>
-      </c>
-      <c r="C42" s="76"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="73"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -2979,17 +2979,15 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="8"/>
     </row>
-    <row r="43" ht="35.25" customHeight="1">
-      <c r="A43" s="77" t="s">
+    <row r="43" ht="30.75" customHeight="1">
+      <c r="A43" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="78">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B37&gt;5, ROUND(B37/5, 0)*5, B37))</f>
-        <v>1445</v>
+      <c r="B43" s="75" t="str">
+        <f>B17</f>
+        <v>AVANTIFEED</v>
       </c>
-      <c r="C43" s="79" t="s">
-        <v>71</v>
-      </c>
+      <c r="C43" s="76"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -3014,20 +3012,16 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="8"/>
     </row>
-    <row r="44" ht="41.25" customHeight="1">
-      <c r="A44" s="80" t="s">
-        <v>72</v>
+    <row r="44" ht="35.25" customHeight="1">
+      <c r="A44" s="77" t="s">
+        <v>71</v>
       </c>
-      <c r="B44" s="81">
-        <f>IFS(
-    B26="Limit", B30,
-    B18="Long", B30+B10*B29,
-    B18="Short", B30-B10*B29
-)</f>
-        <v>1642.6</v>
+      <c r="B44" s="78">
+        <f>IFERROR(IF(OR(B38,B39),0,IF(B37&gt;5,ROUND(B37/5,0)*5,B37)), 0)</f>
+        <v>0</v>
       </c>
       <c r="C44" s="79" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -3053,15 +3047,21 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="8"/>
     </row>
-    <row r="45" ht="43.5" hidden="1" customHeight="1">
+    <row r="45" ht="41.25" customHeight="1">
       <c r="A45" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="81">
+        <f>IFS(
+    B26="Limit", B30,
+    B18="Long", B30+B10*B29,
+    B18="Short", B30-B10*B29
+)</f>
+        <v>0</v>
+      </c>
+      <c r="C45" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="81" t="str">
-        <f>if(B26="Limit", CEILING(B44+B29*B10, B29), "")</f>
-        <v/>
-      </c>
-      <c r="C45" s="82"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -3086,27 +3086,15 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="8"/>
     </row>
-    <row r="46" ht="43.5" customHeight="1">
+    <row r="46" ht="43.5" hidden="1" customHeight="1">
       <c r="A46" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="81">
-        <f>LET(
-  entryPrice, IF(B26="Limit", B45, B44),
-  IF(
-    ISNUMBER(entryPrice),
-    IF(B18="Long",
-      FLOOR(entryPrice-B13*B32,B29),
-      CEILING(entryPrice+B13*B32,B29)
-    ),
-    "⚠️ N/A"
-  )
-)</f>
-        <v>1635.4</v>
+      <c r="B46" s="81" t="str">
+        <f>if(B26="Limit", CEILING(B45+B29*B10, B29), "")</f>
+        <v/>
       </c>
-      <c r="C46" s="82" t="s">
-        <v>76</v>
-      </c>
+      <c r="C46" s="82"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -3133,25 +3121,24 @@
     </row>
     <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="80" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="81">
         <f>LET(
-  entryPrice, IF(B26="Limit", B45, B44),
+  entryPrice, IF(B26="Limit", B46, B45),
   IF(
-    AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),
-    "⚠️ N/A",
-    IF(
-      B18="Long",
-      FLOOR(entryPrice-B32,B29),
-      CEILING(entryPrice+B32,B29)
-    )
+    ISNUMBER(entryPrice),
+    IF(B18="Long",
+      FLOOR(entryPrice-B13*B32,B29),
+      CEILING(entryPrice+B13*B32,B29)
+    ),
+    "⚠️ N/A"
   )
 )</f>
-        <v>1638.4</v>
+        <v>0</v>
       </c>
-      <c r="C47" s="79" t="s">
-        <v>78</v>
+      <c r="C47" s="82" t="s">
+        <v>77</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -3179,25 +3166,21 @@
     </row>
     <row r="48" ht="43.5" customHeight="1">
       <c r="A48" s="80" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B48" s="81">
         <f>LET(
-  entryPrice, IF(B26="Limit", B45, B44),
+  entryPrice, IF(B26="Limit", B46, B45),
   IF(
-    AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),
-    "⚠️ N/A",
-    IF(
-      B18="Long",
-      CEILING(entryPrice+B8*B32,B29),
-      FLOOR(entryPrice-B8*B32,B29)
-    )
+    B18="Long",
+    FLOOR(entryPrice-B32,B29),
+    CEILING(entryPrice+B32,B29)
   )
 )</f>
-        <v>1661.5</v>
+        <v>0</v>
       </c>
       <c r="C48" s="79" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -3223,27 +3206,24 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="8"/>
     </row>
-    <row r="49" ht="51.0" customHeight="1">
+    <row r="49" ht="43.5" customHeight="1">
       <c r="A49" s="80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B49" s="81">
         <f>LET(
-  entryPrice, IF(B26="Limit", B45, B44),
-  IF(
-    AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),
-    "⚠️ N/A",
+  entryPrice, IF(B26="Limit", B46, B45), 
     IF(
       B18="Long",
-      CEILING(entryPrice+B32*B9,B29),
-      FLOOR(entryPrice-B32*B9,B29)
+      CEILING(entryPrice+B8*B32,B29),
+      FLOOR(entryPrice-B8*B32,B29)
     )
   )
-)</f>
-        <v>1693</v>
+</f>
+        <v>0</v>
       </c>
-      <c r="C49" s="82" t="s">
-        <v>82</v>
+      <c r="C49" s="79" t="s">
+        <v>81</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -3269,16 +3249,24 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" ht="36.0" customHeight="1">
-      <c r="A50" s="77" t="s">
-        <v>83</v>
+    <row r="50" ht="51.0" customHeight="1">
+      <c r="A50" s="80" t="s">
+        <v>82</v>
       </c>
-      <c r="B50" s="78">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",ROUND(B12*B43,0))</f>
-        <v>578</v>
+      <c r="B50" s="81">
+        <f>LET(
+  entryPrice, IF(B26="Limit", B46, B45), 
+    IF(
+      B18="Long",
+      CEILING(entryPrice+B32*B9,B29),
+      FLOOR(entryPrice-B32*B9,B29)
+    )
+  )
+</f>
+        <v>0</v>
       </c>
       <c r="C50" s="82" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -3306,14 +3294,14 @@
     </row>
     <row r="51" ht="36.0" customHeight="1">
       <c r="A51" s="77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B51" s="78">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",B43-B50)</f>
-        <v>867</v>
+        <f>IF(OR(B38,B39, B40),0,ROUND(B12*B44,0))</f>
+        <v>0</v>
       </c>
       <c r="C51" s="82" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -3340,15 +3328,15 @@
       <c r="Z51" s="8"/>
     </row>
     <row r="52" ht="36.0" customHeight="1">
-      <c r="A52" s="80" t="s">
+      <c r="A52" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="78">
+        <f>IF(OR(B38,B39,B40),0,B44-B51)</f>
+        <v>0</v>
+      </c>
+      <c r="C52" s="82" t="s">
         <v>87</v>
-      </c>
-      <c r="B52" s="83">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",ROUND((B44-B47)*B43,0),ROUND((B47-B44)*B43,0)))</f>
-        <v>6069</v>
-      </c>
-      <c r="C52" s="79" t="s">
-        <v>88</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -3376,18 +3364,18 @@
     </row>
     <row r="53" ht="36.0" customHeight="1">
       <c r="A53" s="80" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="83">
+        <f>IF(B18="Long",ROUND((B45-B48)*B44,0),ROUND((B48-B45)*B44,0))</f>
+        <v>0</v>
+      </c>
+      <c r="C53" s="79" t="s">
         <v>89</v>
-      </c>
-      <c r="B53" s="84" t="str">
-        <f>ROUND(B52/B15,1) &amp; "R"</f>
-        <v>0.5R</v>
-      </c>
-      <c r="C53" s="82" t="s">
-        <v>90</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
-      <c r="F53" s="70"/>
+      <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
       <c r="I53" s="7"/>
@@ -3410,19 +3398,19 @@
       <c r="Z53" s="8"/>
     </row>
     <row r="54" ht="36.0" customHeight="1">
-      <c r="A54" s="85" t="s">
-        <v>91</v>
+      <c r="A54" s="80" t="s">
+        <v>90</v>
       </c>
-      <c r="B54" s="86">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B19="Long",ROUND((B46-B44)*B43,0),ROUND((B46-B44)*B43,0)))</f>
-        <v>-10404</v>
+      <c r="B54" s="84" t="str">
+        <f>ROUND(B53/B15,1) &amp; "R"</f>
+        <v>0R</v>
       </c>
       <c r="C54" s="82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
+      <c r="F54" s="70"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -3445,15 +3433,15 @@
       <c r="Z54" s="8"/>
     </row>
     <row r="55" ht="36.0" customHeight="1">
-      <c r="A55" s="87" t="s">
+      <c r="A55" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="B55" s="86">
+        <f>IF(B19="Long",ROUND((B47-B45)*B44,0),ROUND((B47-B45)*B44,0))</f>
+        <v>0</v>
+      </c>
+      <c r="C55" s="82" t="s">
         <v>93</v>
-      </c>
-      <c r="B55" s="88" t="str">
-        <f>ROUND(B54/B15,1) &amp; "R"</f>
-        <v>-0.8R</v>
-      </c>
-      <c r="C55" s="89" t="s">
-        <v>94</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -3481,14 +3469,14 @@
     </row>
     <row r="56" ht="36.0" customHeight="1">
       <c r="A56" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" s="88" t="str">
+        <f>ROUND(B55/B15,1) &amp; "R"</f>
+        <v>0R</v>
+      </c>
+      <c r="C56" s="89" t="s">
         <v>95</v>
-      </c>
-      <c r="B56" s="90">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",(B48-B44)*B43,(B44-B48)*B43))</f>
-        <v>27310.5</v>
-      </c>
-      <c r="C56" s="91" t="s">
-        <v>96</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -3516,14 +3504,14 @@
     </row>
     <row r="57" ht="36.0" customHeight="1">
       <c r="A57" s="87" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" s="90">
+        <f>IF(B18="Long",(B49-B45)*B44,(B45-B49)*B44)</f>
+        <v>0</v>
+      </c>
+      <c r="C57" s="91" t="s">
         <v>97</v>
-      </c>
-      <c r="B57" s="92" t="str">
-        <f>ROUND(B56/B15,1) &amp; "R"</f>
-        <v>2.2R</v>
-      </c>
-      <c r="C57" s="89" t="s">
-        <v>98</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -3551,14 +3539,14 @@
     </row>
     <row r="58" ht="36.0" customHeight="1">
       <c r="A58" s="87" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
-      <c r="B58" s="90">
-        <f>IF(AND(B22&gt;0,B23&gt;0,B23/B22&gt;=B11),"⚠️ N/A",IF(B18="Long",(B48-B44)*B50+(B49-B44)*B51,(B44-B48)*B50+(B44-B49)*B51))</f>
-        <v>54621</v>
+      <c r="B58" s="92" t="str">
+        <f>ROUND(B57/B15,1) &amp; "R"</f>
+        <v>0R</v>
       </c>
       <c r="C58" s="89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -3585,15 +3573,15 @@
       <c r="Z58" s="8"/>
     </row>
     <row r="59" ht="36.0" customHeight="1">
-      <c r="A59" s="93" t="s">
+      <c r="A59" s="87" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" s="90">
+        <f>IF(B18="Long",(B49-B45)*B51+(B50-B45)*B52,(B45-B49)*B51+(B45-B50)*B52)</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="89" t="s">
         <v>101</v>
-      </c>
-      <c r="B59" s="94" t="str">
-        <f>ROUND(B58/B15,1) &amp; "R"</f>
-        <v>4.4R</v>
-      </c>
-      <c r="C59" s="95" t="s">
-        <v>102</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -3619,10 +3607,17 @@
       <c r="Y59" s="7"/>
       <c r="Z59" s="8"/>
     </row>
-    <row r="60" ht="21.75" customHeight="1">
-      <c r="A60" s="96"/>
-      <c r="B60" s="97"/>
-      <c r="C60" s="98"/>
+    <row r="60" ht="36.0" customHeight="1">
+      <c r="A60" s="93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" s="94" t="str">
+        <f>ROUND(B59/B15,1) &amp; "R"</f>
+        <v>0R</v>
+      </c>
+      <c r="C60" s="95" t="s">
+        <v>103</v>
+      </c>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -3703,7 +3698,7 @@
       <c r="Y62" s="7"/>
       <c r="Z62" s="8"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="21.75" customHeight="1">
       <c r="A63" s="96"/>
       <c r="B63" s="97"/>
       <c r="C63" s="98"/>
@@ -9192,37 +9187,37 @@
       <c r="Z258" s="8"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="99"/>
-      <c r="B259" s="100"/>
-      <c r="C259" s="101"/>
-      <c r="D259" s="102"/>
-      <c r="E259" s="102"/>
-      <c r="F259" s="102"/>
-      <c r="G259" s="102"/>
-      <c r="H259" s="102"/>
-      <c r="I259" s="102"/>
-      <c r="J259" s="102"/>
-      <c r="K259" s="102"/>
-      <c r="L259" s="102"/>
-      <c r="M259" s="102"/>
-      <c r="N259" s="102"/>
-      <c r="O259" s="102"/>
-      <c r="P259" s="102"/>
-      <c r="Q259" s="102"/>
-      <c r="R259" s="102"/>
-      <c r="S259" s="102"/>
-      <c r="T259" s="102"/>
-      <c r="U259" s="102"/>
-      <c r="V259" s="102"/>
-      <c r="W259" s="102"/>
-      <c r="X259" s="102"/>
-      <c r="Y259" s="102"/>
+      <c r="A259" s="96"/>
+      <c r="B259" s="97"/>
+      <c r="C259" s="98"/>
+      <c r="D259" s="7"/>
+      <c r="E259" s="7"/>
+      <c r="F259" s="7"/>
+      <c r="G259" s="7"/>
+      <c r="H259" s="7"/>
+      <c r="I259" s="7"/>
+      <c r="J259" s="7"/>
+      <c r="K259" s="7"/>
+      <c r="L259" s="7"/>
+      <c r="M259" s="7"/>
+      <c r="N259" s="7"/>
+      <c r="O259" s="7"/>
+      <c r="P259" s="7"/>
+      <c r="Q259" s="7"/>
+      <c r="R259" s="7"/>
+      <c r="S259" s="7"/>
+      <c r="T259" s="7"/>
+      <c r="U259" s="7"/>
+      <c r="V259" s="7"/>
+      <c r="W259" s="7"/>
+      <c r="X259" s="7"/>
+      <c r="Y259" s="7"/>
       <c r="Z259" s="8"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="103"/>
-      <c r="B260" s="102"/>
-      <c r="C260" s="103"/>
+      <c r="A260" s="99"/>
+      <c r="B260" s="100"/>
+      <c r="C260" s="101"/>
       <c r="D260" s="102"/>
       <c r="E260" s="102"/>
       <c r="F260" s="102"/>
@@ -9245,7 +9240,7 @@
       <c r="W260" s="102"/>
       <c r="X260" s="102"/>
       <c r="Y260" s="102"/>
-      <c r="Z260" s="102"/>
+      <c r="Z260" s="8"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="103"/>
@@ -30443,71 +30438,99 @@
       <c r="Y1017" s="102"/>
       <c r="Z1017" s="102"/>
     </row>
+    <row r="1018" ht="15.75" customHeight="1">
+      <c r="A1018" s="103"/>
+      <c r="B1018" s="102"/>
+      <c r="C1018" s="103"/>
+      <c r="D1018" s="102"/>
+      <c r="E1018" s="102"/>
+      <c r="F1018" s="102"/>
+      <c r="G1018" s="102"/>
+      <c r="H1018" s="102"/>
+      <c r="I1018" s="102"/>
+      <c r="J1018" s="102"/>
+      <c r="K1018" s="102"/>
+      <c r="L1018" s="102"/>
+      <c r="M1018" s="102"/>
+      <c r="N1018" s="102"/>
+      <c r="O1018" s="102"/>
+      <c r="P1018" s="102"/>
+      <c r="Q1018" s="102"/>
+      <c r="R1018" s="102"/>
+      <c r="S1018" s="102"/>
+      <c r="T1018" s="102"/>
+      <c r="U1018" s="102"/>
+      <c r="V1018" s="102"/>
+      <c r="W1018" s="102"/>
+      <c r="X1018" s="102"/>
+      <c r="Y1018" s="102"/>
+      <c r="Z1018" s="102"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
-  <conditionalFormatting sqref="B44">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B49">
     <cfRule type="expression" dxfId="0" priority="8">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="expression" dxfId="0" priority="10">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" dxfId="1" priority="11">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" dxfId="0" priority="12">
       <formula>$B18="Short"</formula>
     </cfRule>

--- a/Position Size Calculator.xlsx
+++ b/Position Size Calculator.xlsx
@@ -16,20 +16,6 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B50">
-      <text>
-        <t xml:space="preserve">Legend
-🟠 Orange – SELL
-🔵 Blue – BUY</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="B49">
-      <text>
-        <t xml:space="preserve">Legend
-🟠 Orange – SELL
-🔵 Blue – BUY</t>
-      </text>
-    </comment>
     <comment authorId="0" ref="B48">
       <text>
         <t xml:space="preserve">Legend
@@ -44,7 +30,21 @@
 🔵 Blue – BUY</t>
       </text>
     </comment>
+    <comment authorId="0" ref="B46">
+      <text>
+        <t xml:space="preserve">Legend
+🟠 Orange – SELL
+🔵 Blue – BUY</t>
+      </text>
+    </comment>
     <comment authorId="0" ref="B45">
+      <text>
+        <t xml:space="preserve">Legend
+🟠 Orange – SELL
+🔵 Blue – BUY</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="B43">
       <text>
         <t xml:space="preserve">Legend
 🟠 Orange – SELL
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>📊  Position Size Calculator ( Fill in the required fields marked with * )</t>
   </si>
@@ -139,9 +139,6 @@
     <t>*  Symbol</t>
   </si>
   <si>
-    <t>AVANTIFEED</t>
-  </si>
-  <si>
     <t>Stock Name: Enter the stock name (not case-sensitive). It will be converted to UPPERCASE automatically.</t>
   </si>
   <si>
@@ -157,16 +154,13 @@
     <t>*  Setup</t>
   </si>
   <si>
-    <t>EVB</t>
+    <t>NSE Topers</t>
   </si>
   <si>
     <t>Select Setup: Different setups use different target values based on backtesting.</t>
   </si>
   <si>
-    <t>Mandatory Input Field. Enter high/low of breakout candle</t>
-  </si>
-  <si>
-    <t>Mandatory Input Field. Enter high/low of confirmation candle</t>
+    <t>Mandatory Input Field. Enter high/low of entry candle</t>
   </si>
   <si>
     <t>*  ATR</t>
@@ -180,15 +174,6 @@
   <si>
     <t xml:space="preserve">Upper/Lower Circuit — Trading near these levels carries higher risk.
 </t>
-  </si>
-  <si>
-    <t>*  Entry</t>
-  </si>
-  <si>
-    <t>Confirmation Candle</t>
-  </si>
-  <si>
-    <t>Are you entering at the confirmation candle, or at the breakout candle</t>
   </si>
   <si>
     <t>* Order Type</t>
@@ -801,15 +786,15 @@
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
       <bottom/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFCCCCCC"/>
       </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
       <bottom/>
     </border>
     <border>
@@ -980,49 +965,49 @@
     <xf borderId="8" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="11" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="5" fontId="11" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="5" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="11" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="5" fontId="11" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1031,134 +1016,134 @@
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="5" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="5" fontId="11" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="17" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="13" fillId="5" fontId="11" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="11" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="5" fontId="11" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="5" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="18" fillId="5" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="19" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="19" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="20" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="12" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="18" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="18" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="21" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="21" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="21" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="8" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="6" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="6" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="7" fontId="8" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="7" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="7" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="4" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="7" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="7" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="5" fontId="10" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="5" fontId="10" numFmtId="1" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="8" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="24" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -1169,67 +1154,67 @@
     <xf borderId="27" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="28" fillId="10" fontId="16" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="28" fillId="10" fontId="16" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="10" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="10" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="30" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="30" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="10" fontId="16" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="10" fontId="16" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="29" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="29" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="10" fontId="18" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="10" fontId="18" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="10" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="9" fillId="10" fontId="18" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="31" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="31" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="10" fontId="19" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="10" fontId="19" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="32" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="32" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="10" fontId="19" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="10" fontId="19" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="34" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="34" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="10" fontId="20" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="10" fontId="20" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="34" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="34" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="33" fillId="10" fontId="20" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="33" fillId="10" fontId="20" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="35" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="35" fillId="10" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="36" fillId="10" fontId="20" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="36" fillId="10" fontId="20" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="37" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="37" fillId="5" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1317,7 +1302,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1619250" cy="666750"/>
@@ -1796,16 +1781,16 @@
 IFS(
 B19="NSE Topers",3/B7,
 B19="EMB",2/B7,
-B19="EVB",2/B7
+B19="EVB",2.25/B7
 )
-+IF(B27="Strong",1/B7,0)
-+IF(B26="Market",0.5,0),
++IF(B25="Strong",1/B7,0)
++IF(B24="Market",0.5,0),
 0.25)</f>
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="C8" s="24" t="str">
         <f t="shared" ref="C8:C9" si="1">B8 &amp; "R"</f>
-        <v>4.5R</v>
+        <v>6.5R</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1838,11 +1823,11 @@
       <c r="B9" s="28">
         <f>CEILING(B8*2.5,1)
  </f>
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C9" s="24" t="str">
         <f t="shared" si="1"/>
-        <v>12R</v>
+        <v>17R</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -2103,11 +2088,9 @@
       <c r="A17" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="34" t="s">
         <v>27</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>28</v>
       </c>
       <c r="D17" s="25"/>
       <c r="E17" s="25"/>
@@ -2135,13 +2118,13 @@
     </row>
     <row r="18" ht="46.5" customHeight="1">
       <c r="A18" s="43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="C18" s="34" t="s">
         <v>30</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>31</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -2169,13 +2152,13 @@
     </row>
     <row r="19" ht="46.5" customHeight="1">
       <c r="A19" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="C19" s="47" t="s">
         <v>33</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>34</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -2202,13 +2185,13 @@
       <c r="Z19" s="8"/>
     </row>
     <row r="20" ht="46.5" customHeight="1">
-      <c r="A20" s="45" t="str">
-        <f>IF(B18="Long", "*  Breakout High", "*  Breakout Low")</f>
-        <v>*  Breakout High</v>
+      <c r="A20" s="48" t="str">
+        <f>IF(B18="Long", "*  Entry Candle High", "*  Entry Candle Low")</f>
+        <v>*  Entry Candle High</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="48" t="s">
-        <v>35</v>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50" t="s">
+        <v>34</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -2234,13 +2217,12 @@
       <c r="Y20" s="7"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21" ht="46.5" customHeight="1">
-      <c r="A21" s="49" t="str">
-        <f>IF(B18="Long", "*  Confirmation High", "*  Confirmation Low")</f>
-        <v>*  Confirmation High</v>
+    <row r="21" ht="36.75" customHeight="1">
+      <c r="A21" s="51" t="s">
+        <v>35</v>
       </c>
-      <c r="B21" s="50"/>
-      <c r="C21" s="48" t="s">
+      <c r="B21" s="52"/>
+      <c r="C21" s="18" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="7"/>
@@ -2267,14 +2249,12 @@
       <c r="Y21" s="7"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22" ht="36.75" customHeight="1">
-      <c r="A22" s="51" t="s">
+    <row r="22" ht="52.5" customHeight="1">
+      <c r="A22" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="18" t="s">
-        <v>38</v>
-      </c>
+      <c r="B22" s="54"/>
+      <c r="C22" s="14"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -2300,11 +2280,14 @@
       <c r="Z22" s="8"/>
     </row>
     <row r="23" ht="52.5" customHeight="1">
-      <c r="A23" s="53" t="s">
-        <v>39</v>
+      <c r="A23" s="53" t="str">
+        <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
+        <v>* Upper Circuit</v>
       </c>
       <c r="B23" s="54"/>
-      <c r="C23" s="14"/>
+      <c r="C23" s="55" t="s">
+        <v>38</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -2329,14 +2312,15 @@
       <c r="Y23" s="7"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24" ht="52.5" customHeight="1">
-      <c r="A24" s="53" t="str">
-        <f>IF(B18="Long","* Upper Circuit","* Lower Circuit")</f>
-        <v>* Upper Circuit</v>
+    <row r="24" ht="46.5" customHeight="1">
+      <c r="A24" s="53" t="s">
+        <v>39</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="55" t="s">
+      <c r="B24" s="56" t="s">
         <v>40</v>
+      </c>
+      <c r="C24" s="57" t="s">
+        <v>41</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -2362,15 +2346,15 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25" ht="46.5" customHeight="1">
+    <row r="25" ht="93.0" customHeight="1">
       <c r="A25" s="53" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2396,16 +2380,15 @@
       <c r="Y25" s="7"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26" ht="46.5" customHeight="1">
-      <c r="A26" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="56" t="s">
+    <row r="26" ht="46.5" hidden="1" customHeight="1">
+      <c r="A26" s="58" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="57" t="s">
-        <v>46</v>
+      <c r="B26" s="59">
+        <f>IF(AND(B21&gt;0, B22&gt;0), B22/B21,0)</f>
+        <v>0</v>
       </c>
+      <c r="C26" s="14"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
@@ -2430,16 +2413,20 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27" ht="93.0" customHeight="1">
-      <c r="A27" s="53" t="s">
-        <v>47</v>
+    <row r="27" ht="46.5" hidden="1" customHeight="1">
+      <c r="A27" s="58" t="s">
+        <v>46</v>
       </c>
-      <c r="B27" s="56" t="s">
-        <v>48</v>
+      <c r="B27" s="60">
+        <f>IF(B20&lt;1,0,
+ IF(B20&lt;250,0.01,
+ IF(B20&lt;=1000,0.05,
+ IF(B20&lt;=5000,0.1,
+ IF(B20&lt;=10000,0.5,
+ IF(B20&lt;=20000,1,5))))))</f>
+        <v>0</v>
       </c>
-      <c r="C27" s="57" t="s">
-        <v>49</v>
-      </c>
+      <c r="C27" s="18"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -2465,14 +2452,14 @@
       <c r="Z27" s="8"/>
     </row>
     <row r="28" ht="46.5" hidden="1" customHeight="1">
-      <c r="A28" s="58" t="s">
-        <v>50</v>
+      <c r="A28" s="61" t="s">
+        <v>47</v>
       </c>
-      <c r="B28" s="59">
-        <f>IF(AND(B22&gt;0, B23&gt;0), B23/B22,0)</f>
+      <c r="B28" s="62">
+        <f>IF(ISNUMBER(B20),B20,0)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="14"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -2497,20 +2484,12 @@
       <c r="Y28" s="7"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29" ht="46.5" hidden="1" customHeight="1">
-      <c r="A29" s="58" t="s">
-        <v>51</v>
+    <row r="29" ht="21.75" hidden="1" customHeight="1">
+      <c r="A29" s="5" t="s">
+        <v>48</v>
       </c>
-      <c r="B29" s="60">
-        <f>IF(B21&lt;1,0,
- IF(B21&lt;250,0.01,
- IF(B21&lt;=1000,0.05,
- IF(B21&lt;=5000,0.1,
- IF(B21&lt;=10000,0.5,
- IF(B21&lt;=20000,1,5))))))</f>
-        <v>0</v>
-      </c>
-      <c r="C29" s="18"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -2535,15 +2514,17 @@
       <c r="Y29" s="7"/>
       <c r="Z29" s="8"/>
     </row>
-    <row r="30" ht="46.5" hidden="1" customHeight="1">
-      <c r="A30" s="61" t="s">
-        <v>52</v>
+    <row r="30" ht="21.75" hidden="1" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>49</v>
       </c>
-      <c r="B30" s="62">
-        <f>LET(x,IF(B25="Confirmation Candle",B21,B20),IF(ISNUMBER(x),x,0))</f>
+      <c r="B30" s="63">
+        <f>FLOOR(B21*B7, 0.1)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="18"/>
+      <c r="C30" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -2568,12 +2549,17 @@
       <c r="Y30" s="7"/>
       <c r="Z30" s="8"/>
     </row>
-    <row r="31" ht="21.75" hidden="1" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>53</v>
+    <row r="31" ht="33.0" hidden="1" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>51</v>
       </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+      <c r="B31" s="63">
+        <f>B4*B5</f>
+        <v>12500</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -2600,14 +2586,14 @@
     </row>
     <row r="32" ht="21.75" hidden="1" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B32" s="63">
-        <f>FLOOR(B22*B7, 0.1)</f>
-        <v>0</v>
+        <f>B4*B6</f>
+        <v>2375000</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -2633,16 +2619,16 @@
       <c r="Y32" s="7"/>
       <c r="Z32" s="8"/>
     </row>
-    <row r="33" ht="33.0" hidden="1" customHeight="1">
+    <row r="33" ht="21.75" hidden="1" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
-      <c r="B33" s="63">
-        <f>B4*B5</f>
-        <v>12500</v>
+      <c r="B33" s="64">
+        <f>IF(B30&gt;0,B31/B30,0)</f>
+        <v>0</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -2670,14 +2656,14 @@
     </row>
     <row r="34" ht="21.75" hidden="1" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
-      <c r="B34" s="63">
-        <f>B4*B6</f>
-        <v>2375000</v>
+      <c r="B34" s="64">
+        <f>IF(B28&gt;0, B32/B28, 0)</f>
+        <v>0</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -2704,15 +2690,15 @@
       <c r="Z34" s="8"/>
     </row>
     <row r="35" ht="21.75" hidden="1" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>60</v>
+      <c r="A35" s="19" t="s">
+        <v>59</v>
       </c>
-      <c r="B35" s="64">
-        <f>IF(B32&gt;0,B33/B32,0)</f>
+      <c r="B35" s="65">
+        <f>MIN(B33,B34)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>61</v>
+      <c r="C35" s="21" t="s">
+        <v>60</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -2739,16 +2725,14 @@
       <c r="Z35" s="8"/>
     </row>
     <row r="36" ht="21.75" hidden="1" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>62</v>
+      <c r="A36" s="66" t="s">
+        <v>61</v>
       </c>
-      <c r="B36" s="64">
-        <f>IF(B30&gt;0, B34/B30, 0)</f>
+      <c r="B36" s="67" t="b">
+        <f>B26&gt;B11</f>
         <v>0</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>63</v>
-      </c>
+      <c r="C36" s="68"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -2774,16 +2758,14 @@
       <c r="Z36" s="8"/>
     </row>
     <row r="37" ht="21.75" hidden="1" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>64</v>
+      <c r="A37" s="66" t="s">
+        <v>62</v>
       </c>
-      <c r="B37" s="65">
-        <f>MIN(B35,B36)</f>
+      <c r="B37" s="67" t="b">
+        <f>IF(B23&lt;1,FALSE,IF(B18="Long",(B23-B47)/B23&lt;=B14,(B47-B23)/B23&lt;=B14))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="21" t="s">
-        <v>65</v>
-      </c>
+      <c r="C37" s="68"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
@@ -2810,10 +2792,10 @@
     </row>
     <row r="38" ht="21.75" hidden="1" customHeight="1">
       <c r="A38" s="66" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B38" s="67" t="b">
-        <f>B28&gt;B11</f>
+        <f>IF(B23&lt;1,FALSE,IF(B18="Long",(B23-B48)/B23&lt;=B14,(B48-B23)/B23&lt;=B14))</f>
         <v>0</v>
       </c>
       <c r="C38" s="68"/>
@@ -2841,19 +2823,28 @@
       <c r="Y38" s="7"/>
       <c r="Z38" s="8"/>
     </row>
-    <row r="39" ht="21.75" hidden="1" customHeight="1">
-      <c r="A39" s="66" t="s">
-        <v>67</v>
+    <row r="39" ht="63.0" customHeight="1">
+      <c r="A39" s="69" t="str">
+        <f>IFERROR(
+   IF(B36,
+      "☠️ Spread Too High — High Slippage Risk - DO NOT TRADE",
+      IF(B37,
+         "☠️ T1 near circuit limit — False Breakout / Reversal Risk - DO NOT TRADE",
+         IF(B38,
+            "☠️ T2 near circuit limit — Exit 100% at T1",
+            ""
+         )
+      )
+   ),
+   ""
+)
+</f>
+        <v/>
       </c>
-      <c r="B39" s="67" t="b">
-        <f>IF(B24&lt;1,FALSE,(B24-B49)/B24&lt;=B14)</f>
-        <v>0</v>
-      </c>
-      <c r="C39" s="68"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="G39" s="70"/>
       <c r="H39" s="7"/>
       <c r="I39" s="7"/>
       <c r="J39" s="7"/>
@@ -2874,15 +2865,12 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="8"/>
     </row>
-    <row r="40" ht="21.75" hidden="1" customHeight="1">
-      <c r="A40" s="66" t="s">
-        <v>68</v>
+    <row r="40" ht="40.5" customHeight="1">
+      <c r="A40" s="71" t="s">
+        <v>64</v>
       </c>
-      <c r="B40" s="67" t="b">
-        <f>IF(B24&lt;1,FALSE,(B24-B50)/B24&lt;=B14)</f>
-        <v>0</v>
-      </c>
-      <c r="C40" s="68"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="73"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
@@ -2907,28 +2895,19 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="8"/>
     </row>
-    <row r="41" ht="63.0" customHeight="1">
-      <c r="A41" s="69" t="str">
-        <f>IFERROR(
-   IF(B38,
-      "☠️ Spread Too High — High Slippage Risk - DO NOT TRADE",
-      IF(B39,
-         "☠️ T1 near circuit limit — False Breakout / Reversal Risk - DO NOT TRADE",
-         IF(B40,
-            "☠️ T2 near circuit limit — Exit 100% at T1",
-            ""
-         )
-      )
-   ),
-   ""
-)
-</f>
+    <row r="41" ht="30.75" customHeight="1">
+      <c r="A41" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="75" t="str">
+        <f>B17</f>
         <v/>
       </c>
+      <c r="C41" s="76"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="70"/>
+      <c r="G41" s="7"/>
       <c r="H41" s="7"/>
       <c r="I41" s="7"/>
       <c r="J41" s="7"/>
@@ -2949,12 +2928,17 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="8"/>
     </row>
-    <row r="42" ht="40.5" customHeight="1">
-      <c r="A42" s="71" t="s">
-        <v>69</v>
+    <row r="42" ht="35.25" customHeight="1">
+      <c r="A42" s="77" t="s">
+        <v>66</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="73"/>
+      <c r="B42" s="78">
+        <f>IFERROR(IF(OR(B36,B37),0,IF(B35&gt;5,ROUND(B35/5,0)*5,B35)), 0)</f>
+        <v>0</v>
+      </c>
+      <c r="C42" s="79" t="s">
+        <v>67</v>
+      </c>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
@@ -2979,15 +2963,21 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="8"/>
     </row>
-    <row r="43" ht="30.75" customHeight="1">
-      <c r="A43" s="74" t="s">
-        <v>70</v>
+    <row r="43" ht="41.25" customHeight="1">
+      <c r="A43" s="80" t="s">
+        <v>68</v>
       </c>
-      <c r="B43" s="75" t="str">
-        <f>B17</f>
-        <v>AVANTIFEED</v>
+      <c r="B43" s="81">
+        <f>IFS(
+    B24="Limit", B28,
+    B18="Long", B28+B10*B27,
+    B18="Short", B28-B10*B27
+)</f>
+        <v>0</v>
       </c>
-      <c r="C43" s="76"/>
+      <c r="C43" s="79" t="s">
+        <v>69</v>
+      </c>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
@@ -3012,17 +3002,15 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="8"/>
     </row>
-    <row r="44" ht="35.25" customHeight="1">
-      <c r="A44" s="77" t="s">
-        <v>71</v>
+    <row r="44" ht="43.5" hidden="1" customHeight="1">
+      <c r="A44" s="80" t="s">
+        <v>70</v>
       </c>
-      <c r="B44" s="78">
-        <f>IFERROR(IF(OR(B38,B39),0,IF(B37&gt;5,ROUND(B37/5,0)*5,B37)), 0)</f>
-        <v>0</v>
+      <c r="B44" s="81" t="str">
+        <f>if(B24="Limit", CEILING(B43+B27*B10, B27), "")</f>
+        <v/>
       </c>
-      <c r="C44" s="79" t="s">
-        <v>72</v>
-      </c>
+      <c r="C44" s="82"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
@@ -3047,20 +3035,26 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="8"/>
     </row>
-    <row r="45" ht="41.25" customHeight="1">
+    <row r="45" ht="43.5" customHeight="1">
       <c r="A45" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B45" s="81">
-        <f>IFS(
-    B26="Limit", B30,
-    B18="Long", B30+B10*B29,
-    B18="Short", B30-B10*B29
+        <f>LET(
+  entryPrice, IF(B24="Limit", B44, B43),
+  IF(
+    ISNUMBER(entryPrice),
+    IF(B18="Long",
+      FLOOR(entryPrice-B13*B30,B27),
+      CEILING(entryPrice+B13*B30,B27)
+    ),
+    "⚠️ N/A"
+  )
 )</f>
         <v>0</v>
       </c>
-      <c r="C45" s="79" t="s">
-        <v>74</v>
+      <c r="C45" s="82" t="s">
+        <v>72</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -3086,15 +3080,24 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="8"/>
     </row>
-    <row r="46" ht="43.5" hidden="1" customHeight="1">
+    <row r="46" ht="43.5" customHeight="1">
       <c r="A46" s="80" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
-      <c r="B46" s="81" t="str">
-        <f>if(B26="Limit", CEILING(B45+B29*B10, B29), "")</f>
-        <v/>
+      <c r="B46" s="81">
+        <f>LET(
+  entryPrice, IF(B24="Limit", B44, B43),
+  IF(
+    B18="Long",
+    FLOOR(entryPrice-B30,B27),
+    CEILING(entryPrice+B30,B27)
+  )
+)</f>
+        <v>0</v>
       </c>
-      <c r="C46" s="82"/>
+      <c r="C46" s="79" t="s">
+        <v>74</v>
+      </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
@@ -3121,24 +3124,22 @@
     </row>
     <row r="47" ht="43.5" customHeight="1">
       <c r="A47" s="80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" s="81">
         <f>LET(
-  entryPrice, IF(B26="Limit", B46, B45),
-  IF(
-    ISNUMBER(entryPrice),
-    IF(B18="Long",
-      FLOOR(entryPrice-B13*B32,B29),
-      CEILING(entryPrice+B13*B32,B29)
-    ),
-    "⚠️ N/A"
+  entryPrice, IF(B24="Limit", B44, B43), 
+    IF(
+      B18="Long",
+      CEILING(entryPrice+B8*B30,B27),
+      FLOOR(entryPrice-B8*B30,B27)
+    )
   )
-)</f>
+</f>
         <v>0</v>
       </c>
-      <c r="C47" s="82" t="s">
-        <v>77</v>
+      <c r="C47" s="79" t="s">
+        <v>76</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -3164,23 +3165,24 @@
       <c r="Y47" s="7"/>
       <c r="Z47" s="8"/>
     </row>
-    <row r="48" ht="43.5" customHeight="1">
+    <row r="48" ht="51.0" customHeight="1">
       <c r="A48" s="80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B48" s="81">
         <f>LET(
-  entryPrice, IF(B26="Limit", B46, B45),
-  IF(
-    B18="Long",
-    FLOOR(entryPrice-B32,B29),
-    CEILING(entryPrice+B32,B29)
+  entryPrice, IF(B24="Limit", B44, B43), 
+    IF(
+      B18="Long",
+      CEILING(entryPrice+B30*B9,B27),
+      FLOOR(entryPrice-B30*B9,B27)
+    )
   )
-)</f>
+</f>
         <v>0</v>
       </c>
-      <c r="C48" s="79" t="s">
-        <v>79</v>
+      <c r="C48" s="82" t="s">
+        <v>78</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -3206,24 +3208,16 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="8"/>
     </row>
-    <row r="49" ht="43.5" customHeight="1">
-      <c r="A49" s="80" t="s">
-        <v>80</v>
+    <row r="49" ht="36.0" customHeight="1">
+      <c r="A49" s="77" t="s">
+        <v>79</v>
       </c>
-      <c r="B49" s="81">
-        <f>LET(
-  entryPrice, IF(B26="Limit", B46, B45), 
-    IF(
-      B18="Long",
-      CEILING(entryPrice+B8*B32,B29),
-      FLOOR(entryPrice-B8*B32,B29)
-    )
-  )
-</f>
+      <c r="B49" s="78">
+        <f>IF(OR(B36,B37, B38),0,ROUND(B12*B42,0))</f>
         <v>0</v>
       </c>
-      <c r="C49" s="79" t="s">
-        <v>81</v>
+      <c r="C49" s="82" t="s">
+        <v>80</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -3249,24 +3243,16 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="8"/>
     </row>
-    <row r="50" ht="51.0" customHeight="1">
-      <c r="A50" s="80" t="s">
-        <v>82</v>
+    <row r="50" ht="36.0" customHeight="1">
+      <c r="A50" s="77" t="s">
+        <v>81</v>
       </c>
-      <c r="B50" s="81">
-        <f>LET(
-  entryPrice, IF(B26="Limit", B46, B45), 
-    IF(
-      B18="Long",
-      CEILING(entryPrice+B32*B9,B29),
-      FLOOR(entryPrice-B32*B9,B29)
-    )
-  )
-</f>
+      <c r="B50" s="78">
+        <f>IF(OR(B36,B37,B38),0,B42-B49)</f>
         <v>0</v>
       </c>
       <c r="C50" s="82" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -3293,15 +3279,15 @@
       <c r="Z50" s="8"/>
     </row>
     <row r="51" ht="36.0" customHeight="1">
-      <c r="A51" s="77" t="s">
-        <v>84</v>
+      <c r="A51" s="80" t="s">
+        <v>83</v>
       </c>
-      <c r="B51" s="78">
-        <f>IF(OR(B38,B39, B40),0,ROUND(B12*B44,0))</f>
+      <c r="B51" s="83">
+        <f>IF(B18="Long",ROUND((B43-B46)*B42,0),ROUND((B46-B43)*B42,0))</f>
         <v>0</v>
       </c>
-      <c r="C51" s="82" t="s">
-        <v>85</v>
+      <c r="C51" s="79" t="s">
+        <v>84</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -3328,19 +3314,19 @@
       <c r="Z51" s="8"/>
     </row>
     <row r="52" ht="36.0" customHeight="1">
-      <c r="A52" s="77" t="s">
-        <v>86</v>
+      <c r="A52" s="80" t="s">
+        <v>85</v>
       </c>
-      <c r="B52" s="78">
-        <f>IF(OR(B38,B39,B40),0,B44-B51)</f>
-        <v>0</v>
+      <c r="B52" s="84" t="str">
+        <f>ROUND(B51/B15,1) &amp; "R"</f>
+        <v>0R</v>
       </c>
       <c r="C52" s="82" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
+      <c r="F52" s="70"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
       <c r="I52" s="7"/>
@@ -3363,15 +3349,15 @@
       <c r="Z52" s="8"/>
     </row>
     <row r="53" ht="36.0" customHeight="1">
-      <c r="A53" s="80" t="s">
-        <v>88</v>
+      <c r="A53" s="85" t="s">
+        <v>87</v>
       </c>
-      <c r="B53" s="83">
-        <f>IF(B18="Long",ROUND((B45-B48)*B44,0),ROUND((B48-B45)*B44,0))</f>
+      <c r="B53" s="86">
+        <f>IF(B19="Long",ROUND((B45-B43)*B42,0),ROUND((B45-B43)*B42,0))</f>
         <v>0</v>
       </c>
-      <c r="C53" s="79" t="s">
-        <v>89</v>
+      <c r="C53" s="82" t="s">
+        <v>88</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -3398,19 +3384,19 @@
       <c r="Z53" s="8"/>
     </row>
     <row r="54" ht="36.0" customHeight="1">
-      <c r="A54" s="80" t="s">
-        <v>90</v>
+      <c r="A54" s="87" t="s">
+        <v>89</v>
       </c>
-      <c r="B54" s="84" t="str">
+      <c r="B54" s="88" t="str">
         <f>ROUND(B53/B15,1) &amp; "R"</f>
         <v>0R</v>
       </c>
-      <c r="C54" s="82" t="s">
-        <v>91</v>
+      <c r="C54" s="89" t="s">
+        <v>90</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
-      <c r="F54" s="70"/>
+      <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
       <c r="I54" s="7"/>
@@ -3433,15 +3419,15 @@
       <c r="Z54" s="8"/>
     </row>
     <row r="55" ht="36.0" customHeight="1">
-      <c r="A55" s="85" t="s">
-        <v>92</v>
+      <c r="A55" s="87" t="s">
+        <v>91</v>
       </c>
-      <c r="B55" s="86">
-        <f>IF(B19="Long",ROUND((B47-B45)*B44,0),ROUND((B47-B45)*B44,0))</f>
+      <c r="B55" s="90">
+        <f>IF(B18="Long",(B47-B43)*B42,(B43-B47)*B42)</f>
         <v>0</v>
       </c>
-      <c r="C55" s="82" t="s">
-        <v>93</v>
+      <c r="C55" s="91" t="s">
+        <v>92</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -3469,14 +3455,14 @@
     </row>
     <row r="56" ht="36.0" customHeight="1">
       <c r="A56" s="87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
-      <c r="B56" s="88" t="str">
+      <c r="B56" s="92" t="str">
         <f>ROUND(B55/B15,1) &amp; "R"</f>
         <v>0R</v>
       </c>
       <c r="C56" s="89" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -3504,14 +3490,14 @@
     </row>
     <row r="57" ht="36.0" customHeight="1">
       <c r="A57" s="87" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B57" s="90">
-        <f>IF(B18="Long",(B49-B45)*B44,(B45-B49)*B44)</f>
+        <f>IF(B18="Long",(B47-B43)*B49+(B48-B43)*B50,(B43-B47)*B49+(B43-B48)*B50)</f>
         <v>0</v>
       </c>
-      <c r="C57" s="91" t="s">
-        <v>97</v>
+      <c r="C57" s="89" t="s">
+        <v>96</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -3538,15 +3524,15 @@
       <c r="Z57" s="8"/>
     </row>
     <row r="58" ht="36.0" customHeight="1">
-      <c r="A58" s="87" t="s">
-        <v>98</v>
+      <c r="A58" s="93" t="s">
+        <v>97</v>
       </c>
-      <c r="B58" s="92" t="str">
+      <c r="B58" s="94" t="str">
         <f>ROUND(B57/B15,1) &amp; "R"</f>
         <v>0R</v>
       </c>
-      <c r="C58" s="89" t="s">
-        <v>99</v>
+      <c r="C58" s="95" t="s">
+        <v>98</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -3572,17 +3558,10 @@
       <c r="Y58" s="7"/>
       <c r="Z58" s="8"/>
     </row>
-    <row r="59" ht="36.0" customHeight="1">
-      <c r="A59" s="87" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" s="90">
-        <f>IF(B18="Long",(B49-B45)*B51+(B50-B45)*B52,(B45-B49)*B51+(B45-B50)*B52)</f>
-        <v>0</v>
-      </c>
-      <c r="C59" s="89" t="s">
-        <v>101</v>
-      </c>
+    <row r="59" ht="21.75" customHeight="1">
+      <c r="A59" s="96"/>
+      <c r="B59" s="97"/>
+      <c r="C59" s="98"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
       <c r="F59" s="7"/>
@@ -3607,17 +3586,10 @@
       <c r="Y59" s="7"/>
       <c r="Z59" s="8"/>
     </row>
-    <row r="60" ht="36.0" customHeight="1">
-      <c r="A60" s="93" t="s">
-        <v>102</v>
-      </c>
-      <c r="B60" s="94" t="str">
-        <f>ROUND(B59/B15,1) &amp; "R"</f>
-        <v>0R</v>
-      </c>
-      <c r="C60" s="95" t="s">
-        <v>103</v>
-      </c>
+    <row r="60" ht="21.75" customHeight="1">
+      <c r="A60" s="96"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="98"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
       <c r="F60" s="7"/>
@@ -3670,7 +3642,7 @@
       <c r="Y61" s="7"/>
       <c r="Z61" s="8"/>
     </row>
-    <row r="62" ht="21.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="96"/>
       <c r="B62" s="97"/>
       <c r="C62" s="98"/>
@@ -3698,7 +3670,7 @@
       <c r="Y62" s="7"/>
       <c r="Z62" s="8"/>
     </row>
-    <row r="63" ht="21.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="96"/>
       <c r="B63" s="97"/>
       <c r="C63" s="98"/>
@@ -9159,65 +9131,65 @@
       <c r="Z257" s="8"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="96"/>
-      <c r="B258" s="97"/>
-      <c r="C258" s="98"/>
-      <c r="D258" s="7"/>
-      <c r="E258" s="7"/>
-      <c r="F258" s="7"/>
-      <c r="G258" s="7"/>
-      <c r="H258" s="7"/>
-      <c r="I258" s="7"/>
-      <c r="J258" s="7"/>
-      <c r="K258" s="7"/>
-      <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
-      <c r="N258" s="7"/>
-      <c r="O258" s="7"/>
-      <c r="P258" s="7"/>
-      <c r="Q258" s="7"/>
-      <c r="R258" s="7"/>
-      <c r="S258" s="7"/>
-      <c r="T258" s="7"/>
-      <c r="U258" s="7"/>
-      <c r="V258" s="7"/>
-      <c r="W258" s="7"/>
-      <c r="X258" s="7"/>
-      <c r="Y258" s="7"/>
+      <c r="A258" s="99"/>
+      <c r="B258" s="100"/>
+      <c r="C258" s="101"/>
+      <c r="D258" s="102"/>
+      <c r="E258" s="102"/>
+      <c r="F258" s="102"/>
+      <c r="G258" s="102"/>
+      <c r="H258" s="102"/>
+      <c r="I258" s="102"/>
+      <c r="J258" s="102"/>
+      <c r="K258" s="102"/>
+      <c r="L258" s="102"/>
+      <c r="M258" s="102"/>
+      <c r="N258" s="102"/>
+      <c r="O258" s="102"/>
+      <c r="P258" s="102"/>
+      <c r="Q258" s="102"/>
+      <c r="R258" s="102"/>
+      <c r="S258" s="102"/>
+      <c r="T258" s="102"/>
+      <c r="U258" s="102"/>
+      <c r="V258" s="102"/>
+      <c r="W258" s="102"/>
+      <c r="X258" s="102"/>
+      <c r="Y258" s="102"/>
       <c r="Z258" s="8"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="96"/>
-      <c r="B259" s="97"/>
-      <c r="C259" s="98"/>
-      <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
-      <c r="G259" s="7"/>
-      <c r="H259" s="7"/>
-      <c r="I259" s="7"/>
-      <c r="J259" s="7"/>
-      <c r="K259" s="7"/>
-      <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
-      <c r="N259" s="7"/>
-      <c r="O259" s="7"/>
-      <c r="P259" s="7"/>
-      <c r="Q259" s="7"/>
-      <c r="R259" s="7"/>
-      <c r="S259" s="7"/>
-      <c r="T259" s="7"/>
-      <c r="U259" s="7"/>
-      <c r="V259" s="7"/>
-      <c r="W259" s="7"/>
-      <c r="X259" s="7"/>
-      <c r="Y259" s="7"/>
-      <c r="Z259" s="8"/>
+      <c r="A259" s="103"/>
+      <c r="B259" s="102"/>
+      <c r="C259" s="103"/>
+      <c r="D259" s="102"/>
+      <c r="E259" s="102"/>
+      <c r="F259" s="102"/>
+      <c r="G259" s="102"/>
+      <c r="H259" s="102"/>
+      <c r="I259" s="102"/>
+      <c r="J259" s="102"/>
+      <c r="K259" s="102"/>
+      <c r="L259" s="102"/>
+      <c r="M259" s="102"/>
+      <c r="N259" s="102"/>
+      <c r="O259" s="102"/>
+      <c r="P259" s="102"/>
+      <c r="Q259" s="102"/>
+      <c r="R259" s="102"/>
+      <c r="S259" s="102"/>
+      <c r="T259" s="102"/>
+      <c r="U259" s="102"/>
+      <c r="V259" s="102"/>
+      <c r="W259" s="102"/>
+      <c r="X259" s="102"/>
+      <c r="Y259" s="102"/>
+      <c r="Z259" s="102"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="99"/>
-      <c r="B260" s="100"/>
-      <c r="C260" s="101"/>
+      <c r="A260" s="103"/>
+      <c r="B260" s="102"/>
+      <c r="C260" s="103"/>
       <c r="D260" s="102"/>
       <c r="E260" s="102"/>
       <c r="F260" s="102"/>
@@ -9240,7 +9212,7 @@
       <c r="W260" s="102"/>
       <c r="X260" s="102"/>
       <c r="Y260" s="102"/>
-      <c r="Z260" s="8"/>
+      <c r="Z260" s="102"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="103"/>
@@ -30410,127 +30382,71 @@
       <c r="Y1016" s="102"/>
       <c r="Z1016" s="102"/>
     </row>
-    <row r="1017" ht="15.75" customHeight="1">
-      <c r="A1017" s="103"/>
-      <c r="B1017" s="102"/>
-      <c r="C1017" s="103"/>
-      <c r="D1017" s="102"/>
-      <c r="E1017" s="102"/>
-      <c r="F1017" s="102"/>
-      <c r="G1017" s="102"/>
-      <c r="H1017" s="102"/>
-      <c r="I1017" s="102"/>
-      <c r="J1017" s="102"/>
-      <c r="K1017" s="102"/>
-      <c r="L1017" s="102"/>
-      <c r="M1017" s="102"/>
-      <c r="N1017" s="102"/>
-      <c r="O1017" s="102"/>
-      <c r="P1017" s="102"/>
-      <c r="Q1017" s="102"/>
-      <c r="R1017" s="102"/>
-      <c r="S1017" s="102"/>
-      <c r="T1017" s="102"/>
-      <c r="U1017" s="102"/>
-      <c r="V1017" s="102"/>
-      <c r="W1017" s="102"/>
-      <c r="X1017" s="102"/>
-      <c r="Y1017" s="102"/>
-      <c r="Z1017" s="102"/>
-    </row>
-    <row r="1018" ht="15.75" customHeight="1">
-      <c r="A1018" s="103"/>
-      <c r="B1018" s="102"/>
-      <c r="C1018" s="103"/>
-      <c r="D1018" s="102"/>
-      <c r="E1018" s="102"/>
-      <c r="F1018" s="102"/>
-      <c r="G1018" s="102"/>
-      <c r="H1018" s="102"/>
-      <c r="I1018" s="102"/>
-      <c r="J1018" s="102"/>
-      <c r="K1018" s="102"/>
-      <c r="L1018" s="102"/>
-      <c r="M1018" s="102"/>
-      <c r="N1018" s="102"/>
-      <c r="O1018" s="102"/>
-      <c r="P1018" s="102"/>
-      <c r="Q1018" s="102"/>
-      <c r="R1018" s="102"/>
-      <c r="S1018" s="102"/>
-      <c r="T1018" s="102"/>
-      <c r="U1018" s="102"/>
-      <c r="V1018" s="102"/>
-      <c r="W1018" s="102"/>
-      <c r="X1018" s="102"/>
-      <c r="Y1018" s="102"/>
-      <c r="Z1018" s="102"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
   </mergeCells>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B43">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45">
+  <conditionalFormatting sqref="B43">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B44">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B46">
+  <conditionalFormatting sqref="B44">
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
+  <conditionalFormatting sqref="B46">
     <cfRule type="expression" dxfId="0" priority="6">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" dxfId="1" priority="7">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B47">
     <cfRule type="expression" dxfId="0" priority="8">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="1" priority="9">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B48">
     <cfRule type="expression" dxfId="0" priority="10">
       <formula>$B18="Short"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" dxfId="1" priority="11">
       <formula>$B18="Long"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B47">
+  <conditionalFormatting sqref="B45">
     <cfRule type="expression" dxfId="0" priority="12">
       <formula>$B18="Short"</formula>
     </cfRule>
@@ -30542,14 +30458,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B19">
       <formula1>"NSE Topers,EMB,EVB"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B26">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B24">
       <formula1>"Limit,Market"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B27">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
       <formula1>"Normal,Strong"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B25">
-      <formula1>"Confirmation Candle,Breakout Candle"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
